--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487738_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487738_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.2165</v>
+        <v>8.3583</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4922</v>
+        <v>6.852</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7244</v>
+        <v>1.5063</v>
       </c>
       <c r="G2" t="n">
         <v>2.4722</v>
@@ -610,13 +610,13 @@
         <v>1.7463</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6667</v>
+        <v>-0.1915</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3779</v>
+        <v>-0.2622</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2887</v>
+        <v>0.0707</v>
       </c>
       <c r="V2" t="n">
         <v>4.3313</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9967</v>
+        <v>2.8754</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1119</v>
+        <v>3.0723</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1151</v>
+        <v>-0.1969</v>
       </c>
       <c r="G3" t="n">
         <v>-0.4165</v>
@@ -688,13 +688,13 @@
         <v>2.1344</v>
       </c>
       <c r="S3" t="n">
-        <v>0.273</v>
+        <v>0.1517</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1357</v>
+        <v>0.0961</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1373</v>
+        <v>0.0556</v>
       </c>
       <c r="V3" t="n">
         <v>1.0059</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5999</v>
+        <v>1.4024</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1539</v>
+        <v>0.8746</v>
       </c>
       <c r="F4" t="n">
-        <v>0.446</v>
+        <v>0.5278</v>
       </c>
       <c r="G4" t="n">
         <v>0.5079</v>
@@ -766,13 +766,13 @@
         <v>1.7463</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2483</v>
+        <v>-0.4458</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4991</v>
+        <v>0.2198</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7474</v>
+        <v>-0.6656</v>
       </c>
       <c r="V4" t="n">
         <v>0.5642</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. VIDAL RODRIGUEZ</t>
+          <t>A. SANTANA OJEDA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6625</v>
+        <v>0.9868</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6194</v>
+        <v>0.1462</v>
       </c>
       <c r="F5" t="n">
-        <v>0.043</v>
+        <v>0.8406</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7864</v>
+        <v>0.4992</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0183</v>
+        <v>1.0381</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2319</v>
+        <v>-0.5389</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0704</v>
+        <v>1.5305</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0298</v>
+        <v>1.5077</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0406</v>
+        <v>0.0228</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.284</v>
+        <v>-1.0313</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0115</v>
+        <v>-0.4696</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2725</v>
+        <v>-0.5617</v>
       </c>
       <c r="P5" t="n">
-        <v>0.194</v>
+        <v>0.9702</v>
       </c>
       <c r="Q5" t="n">
+        <v>-0.9702</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.9403</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.4825</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.4142</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.0684</v>
+      </c>
+      <c r="V5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.0119</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.1211</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-0.3299</v>
-      </c>
       <c r="W5" t="n">
-        <v>-0.3299</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. SANTANA OJEDA</t>
+          <t>E. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4624</v>
+        <v>0.608</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2147</v>
+        <v>0.6194</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6771</v>
+        <v>-0.0115</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4992</v>
+        <v>0.7864</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0381</v>
+        <v>1.0183</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5389</v>
+        <v>-0.2319</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5305</v>
+        <v>1.0704</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5077</v>
+        <v>1.0298</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0228</v>
+        <v>0.0406</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0313</v>
+        <v>-0.284</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4696</v>
+        <v>-0.0115</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5617</v>
+        <v>-0.2725</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9702</v>
+        <v>0.194</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9403</v>
+        <v>0.194</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0069</v>
+        <v>-0.0426</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.775</v>
+        <v>-0.1211</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2319</v>
+        <v>0.0785</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2729</v>
+        <v>0.5208</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6312</v>
+        <v>0.5521</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3583</v>
+        <v>-0.0313</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0813</v>
@@ -1000,13 +1000,13 @@
         <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004</v>
+        <v>0.2484</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3017</v>
+        <v>-0.3808</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3022</v>
+        <v>0.6292</v>
       </c>
       <c r="V7" t="n">
         <v>0.1597</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5891</v>
+        <v>-1.3406</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8568</v>
+        <v>-1.6356</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2677</v>
+        <v>0.295</v>
       </c>
       <c r="G8" t="n">
         <v>0.145</v>
@@ -1078,13 +1078,13 @@
         <v>0.9702</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0182</v>
+        <v>0.2667</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0595</v>
+        <v>0.1618</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0776</v>
+        <v>0.1049</v>
       </c>
       <c r="V8" t="n">
         <v>-0.7821</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.185</v>
+        <v>-1.8904</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9234</v>
+        <v>-1.9014</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2616</v>
+        <v>0.011</v>
       </c>
       <c r="G9" t="n">
         <v>-2.7375</v>
@@ -1156,13 +1156,13 @@
         <v>1.3582</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0431</v>
+        <v>0.2515</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7145</v>
+        <v>0.3076</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3286</v>
+        <v>-0.0561</v>
       </c>
       <c r="V9" t="n">
         <v>0.2075</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1917</v>
+        <v>-3.3248</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5649</v>
+        <v>-3.3437</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3732</v>
+        <v>0.0189</v>
       </c>
       <c r="G10" t="n">
         <v>-2.2622</v>
@@ -1234,13 +1234,13 @@
         <v>0.7761</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3571</v>
+        <v>0.224</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2412</v>
+        <v>-0.0199</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.244</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1224</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8224</v>
+        <v>-3.8648</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4517</v>
+        <v>-1.3306</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3706</v>
+        <v>-2.5342</v>
       </c>
       <c r="G11" t="n">
         <v>1.4255</v>
@@ -1312,13 +1312,13 @@
         <v>1.5523</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0926</v>
+        <v>-1.135</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2113</v>
+        <v>-1.0902</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1187</v>
+        <v>-0.0448</v>
       </c>
       <c r="V11" t="n">
         <v>-3.7672</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.4227</v>
+        <v>4.3311</v>
       </c>
       <c r="E12" t="n">
-        <v>2.997100000000002</v>
+        <v>3.905299999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4258000000000002</v>
+        <v>0.4257</v>
       </c>
       <c r="G12" t="n">
         <v>0.3386999999999998</v>
@@ -1381,7 +1381,7 @@
         <v>-4.226699999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>3.880599999999999</v>
+        <v>3.8806</v>
       </c>
       <c r="Q12" t="n">
         <v>-9.701699999999999</v>
@@ -1390,13 +1390,13 @@
         <v>13.5823</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.0636</v>
+        <v>-1.1551</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.4116</v>
+        <v>-1.5031</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3479000000000002</v>
+        <v>0.3479999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>1.266999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.8137</v>
+        <v>2.8376</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1935</v>
+        <v>1.8932</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6202</v>
+        <v>0.9444</v>
       </c>
       <c r="G13" t="n">
         <v>3.2392</v>
@@ -1468,13 +1468,13 @@
         <v>0.7761</v>
       </c>
       <c r="S13" t="n">
-        <v>0.079</v>
+        <v>0.1029</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5473</v>
+        <v>0.247</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4683</v>
+        <v>-0.1441</v>
       </c>
       <c r="V13" t="n">
         <v>0.6597</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.87</v>
+        <v>2.7159</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1442</v>
+        <v>0.7447</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7258</v>
+        <v>1.9711</v>
       </c>
       <c r="G14" t="n">
         <v>-0.2349</v>
@@ -1546,13 +1546,13 @@
         <v>1.5523</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0489</v>
+        <v>-0.203</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8356</v>
+        <v>-0.235</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2133</v>
+        <v>0.032</v>
       </c>
       <c r="V14" t="n">
         <v>1.6015</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5518</v>
+        <v>0.4611</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1211</v>
+        <v>-0.021</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.4821</v>
       </c>
       <c r="G15" t="n">
         <v>0.5948</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0431</v>
+        <v>-0.1337</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1211</v>
+        <v>-0.021</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0781</v>
+        <v>-0.1127</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>S. GACIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3336</v>
+        <v>0.1289</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1602</v>
+        <v>1.0501</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8266</v>
+        <v>-0.9212</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1642</v>
+        <v>-0.3047</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.478</v>
+        <v>-1.8941</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6422</v>
+        <v>1.5894</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6023</v>
+        <v>2.1577</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7498</v>
+        <v>1.3635</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8525</v>
+        <v>0.7942</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4381</v>
+        <v>-2.4624</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.2278</v>
+        <v>-3.2576</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7897</v>
+        <v>0.7952</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5821</v>
+        <v>-0.194</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3582</v>
+        <v>0.7761</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9172</v>
+        <v>0.5798</v>
       </c>
       <c r="T16" t="n">
-        <v>1.652</v>
+        <v>-0.1374</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2652</v>
+        <v>0.7173</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.1657</v>
+        <v>0.0478</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8462</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.0119</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. GACIC</t>
+          <t>C. UNANUE CEGARRA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2229</v>
+        <v>-0.7607</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2503</v>
+        <v>0.6327</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0274</v>
+        <v>-1.3933</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3047</v>
+        <v>1.2129</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8941</v>
+        <v>-2.3291</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5894</v>
+        <v>3.542</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1577</v>
+        <v>2.9411</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3635</v>
+        <v>0.5891</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7942</v>
+        <v>2.3519</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.4624</v>
+        <v>-1.7281</v>
       </c>
       <c r="N17" t="n">
-        <v>-3.2576</v>
+        <v>-2.9182</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7952</v>
+        <v>1.1901</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.194</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6738</v>
+        <v>-0.5572</v>
       </c>
       <c r="T17" t="n">
-        <v>0.06279999999999999</v>
+        <v>-0.2919</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6111</v>
+        <v>-0.2652</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0478</v>
+        <v>0.3299</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0478</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. VICENTE VIANA</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8391</v>
+        <v>-0.9761</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1761</v>
+        <v>1.2593</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0152</v>
+        <v>-2.2354</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.3427</v>
+        <v>0.1642</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0702</v>
+        <v>-1.478</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2725</v>
+        <v>1.6422</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.395</v>
+        <v>1.6023</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1277</v>
+        <v>0.7498</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5227000000000001</v>
+        <v>0.8525</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9477</v>
+        <v>-1.4381</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1979</v>
+        <v>-2.2278</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2502</v>
+        <v>0.7897</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3881</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R18" t="n">
         <v>1.3582</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6797</v>
+        <v>1.6075</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3174</v>
+        <v>0.7511</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3623</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5642</v>
+        <v>-2.1657</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2239</v>
+        <v>0.8462</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.788</v>
+        <v>-3.0119</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. ABOUBACAR HIMA</t>
+          <t>C. KLOTZ MAROTO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1589</v>
+        <v>-1.1598</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9403</v>
+        <v>-1.0469</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7815</v>
+        <v>-0.1129</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3518</v>
+        <v>-1.866</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4797</v>
+        <v>-0.8683999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1279</v>
+        <v>-0.9977</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3347</v>
+        <v>-0.7179</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3347</v>
+        <v>0.5355</v>
       </c>
       <c r="L19" t="n">
+        <v>-1.2535</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-1.1481</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-1.4039</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.2558</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.1642</v>
+      </c>
+      <c r="Q19" t="n">
         <v>0</v>
       </c>
-      <c r="M19" t="n">
-        <v>-0.0171</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-0.145</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.1279</v>
-      </c>
-      <c r="P19" t="n">
-        <v>-0.7761</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-0.9702</v>
-      </c>
       <c r="R19" t="n">
-        <v>0.194</v>
+        <v>1.1642</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3093</v>
+        <v>0.1063</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3645</v>
+        <v>-0.3289</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0552</v>
+        <v>0.4352</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6597</v>
+        <v>-0.5642</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6597</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. UNANUE CEGARRA</t>
+          <t>A. VICENTE VIANA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6032</v>
+        <v>-1.2062</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3324</v>
+        <v>-0.3244</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9356</v>
+        <v>-0.8817</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2129</v>
+        <v>-1.3427</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.3291</v>
+        <v>-1.0702</v>
       </c>
       <c r="I20" t="n">
-        <v>3.542</v>
+        <v>-0.2725</v>
       </c>
       <c r="J20" t="n">
-        <v>2.9411</v>
+        <v>-0.395</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5891</v>
+        <v>0.1277</v>
       </c>
       <c r="L20" t="n">
-        <v>2.3519</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7281</v>
+        <v>-0.9477</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.9182</v>
+        <v>-1.1979</v>
       </c>
       <c r="O20" t="n">
-        <v>1.1901</v>
+        <v>0.2502</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.7463</v>
+        <v>0.3881</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1642</v>
+        <v>1.3582</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3997</v>
+        <v>0.3126</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.1831</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8075</v>
+        <v>0.4958</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3299</v>
+        <v>-0.5642</v>
       </c>
       <c r="W20" t="n">
-        <v>0.894</v>
+        <v>1.2239</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5642</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. KLOTZ MAROTO</t>
+          <t>S. ABOUBACAR HIMA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8604</v>
+        <v>-1.5865</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7476</v>
+        <v>-2.3407</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1129</v>
+        <v>0.7542</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.866</v>
+        <v>-1.3518</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8683999999999999</v>
+        <v>-1.4797</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9977</v>
+        <v>0.1279</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7179</v>
+        <v>-1.3347</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5355</v>
+        <v>-1.3347</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2535</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1481</v>
+        <v>-0.0171</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4039</v>
+        <v>-0.145</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2558</v>
+        <v>0.1279</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1642</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1642</v>
+        <v>0.194</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5944</v>
+        <v>-0.1183</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0296</v>
+        <v>-0.0359</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4352</v>
+        <v>-0.0824</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5642</v>
+        <v>0.6597</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5642</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7529</v>
+        <v>-3.2096</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8733</v>
+        <v>-2.2727</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8796</v>
+        <v>-0.9369</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4497</v>
@@ -2170,13 +2170,13 @@
         <v>1.3582</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4908</v>
+        <v>1.0341</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7134</v>
+        <v>-0.1128</v>
       </c>
       <c r="U22" t="n">
-        <v>1.2042</v>
+        <v>1.1468</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2716</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4225</v>
+        <v>-2.755400000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4256000000000006</v>
+        <v>-0.4256999999999995</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9969</v>
+        <v>-2.3296</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3387000000000002</v>
+        <v>-0.3387000000000007</v>
       </c>
       <c r="H23" t="n">
         <v>-11.1553</v>
@@ -2221,13 +2221,13 @@
         <v>10.8165</v>
       </c>
       <c r="J23" t="n">
-        <v>8.140499999999999</v>
+        <v>8.140500000000001</v>
       </c>
       <c r="K23" t="n">
         <v>3.9135</v>
       </c>
       <c r="L23" t="n">
-        <v>4.226700000000001</v>
+        <v>4.2267</v>
       </c>
       <c r="M23" t="n">
         <v>-8.478999999999999</v>
@@ -2236,28 +2236,28 @@
         <v>-15.0688</v>
       </c>
       <c r="O23" t="n">
-        <v>6.5899</v>
+        <v>6.589900000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.880500000000001</v>
+        <v>-3.8805</v>
       </c>
       <c r="Q23" t="n">
         <v>-13.5823</v>
       </c>
       <c r="R23" t="n">
-        <v>9.701499999999999</v>
+        <v>9.701500000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>2.0637</v>
+        <v>2.731</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3479000000000001</v>
+        <v>-0.3479</v>
       </c>
       <c r="U23" t="n">
-        <v>2.4118</v>
+        <v>3.0791</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.267100000000001</v>
+        <v>-1.2671</v>
       </c>
       <c r="W23" t="n">
         <v>5.364100000000001</v>
